--- a/artfynd/A 3902-2024 artfynd.xlsx
+++ b/artfynd/A 3902-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 3902-2024 artfynd.xlsx
+++ b/artfynd/A 3902-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>99045864</v>
+        <v>115822418</v>
       </c>
       <c r="B2" t="n">
-        <v>56311</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100067</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,28 +703,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>2K</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Myggsjön, Nrk</t>
+          <t>Skenebäcksmossen, SV Djupsjön, Regna s:n, Nrk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>533645.6650280055</v>
+        <v>533347</v>
       </c>
       <c r="R2" t="n">
-        <v>6531832.173381048</v>
+        <v>6531750</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -756,22 +745,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-03-11</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>15:20</t>
+          <t>2021-07-25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-03-11</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>15:20</t>
+          <t>2021-07-25</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Födosöksspår på tall.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,81 +770,71 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Thomas Strid</t>
+          <t>Sara Elg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Thomas Strid</t>
+          <t>Sara Elg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>101620527</v>
+        <v>99045864</v>
       </c>
       <c r="B3" t="n">
-        <v>56632</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57899</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103012</v>
+        <v>100067</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2K</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skenbäcksmossen, Atlasruta 09F6h (Namnlös), Nrk</t>
+          <t>Myggsjön, Nrk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>533551.8423459081</v>
+        <v>533646</v>
       </c>
       <c r="R3" t="n">
-        <v>6531795.728226202</v>
+        <v>6531832</v>
       </c>
       <c r="S3" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,22 +858,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-06-13</t>
+          <t>2022-03-11</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-06-13</t>
+          <t>2022-03-11</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,49 +888,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ronnie Lindqvist</t>
+          <t>Thomas Strid</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ronnie Lindqvist</t>
+          <t>Thomas Strid</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>101620745</v>
+        <v>101620744</v>
       </c>
       <c r="B4" t="n">
-        <v>57064</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58129</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103055</v>
+        <v>102623</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Trädlärka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Lullula arborea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -972,7 +941,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -982,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>533551.8423459081</v>
+        <v>533552</v>
       </c>
       <c r="R4" t="n">
-        <v>6531795.728226202</v>
+        <v>6531796</v>
       </c>
       <c r="S4" t="n">
         <v>75</v>
@@ -1057,16 +1026,11 @@
         <v>101620526</v>
       </c>
       <c r="B5" t="n">
-        <v>55667</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57774</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1105,10 +1069,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>533551.8423459081</v>
+        <v>533552</v>
       </c>
       <c r="R5" t="n">
-        <v>6531795.728226202</v>
+        <v>6531796</v>
       </c>
       <c r="S5" t="n">
         <v>75</v>
@@ -1177,53 +1141,64 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>115822646</v>
+        <v>101620527</v>
       </c>
       <c r="B6" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58238</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>103012</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Myggsjön, Regna s:n, Nrk</t>
+          <t>Skenbäcksmossen, Atlasruta 09F6h (Namnlös), Nrk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>533434</v>
+        <v>533552</v>
       </c>
       <c r="R6" t="n">
-        <v>6531571</v>
+        <v>6531796</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1247,12 +1222,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-07-25</t>
+          <t>2022-06-13</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-07-25</t>
+          <t>2022-06-13</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1267,65 +1252,76 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Sara Elg</t>
+          <t>Ronnie Lindqvist</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Sara Elg</t>
+          <t>Ronnie Lindqvist</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>115822419</v>
+        <v>101620745</v>
       </c>
       <c r="B7" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58676</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>103055</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skenebäcksmossen, SV Djupsjön, Regna s:n, Nrk</t>
+          <t>Skenbäcksmossen, Atlasruta 09F6h (Namnlös), Nrk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>533674</v>
+        <v>533552</v>
       </c>
       <c r="R7" t="n">
-        <v>6531835</v>
+        <v>6531796</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1349,12 +1345,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2021-07-25</t>
+          <t>2022-06-13</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2021-07-25</t>
+          <t>2022-06-13</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1369,12 +1375,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Sara Elg</t>
+          <t>Ronnie Lindqvist</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Sara Elg</t>
+          <t>Ronnie Lindqvist</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1384,12 +1390,7 @@
         <v>115822647</v>
       </c>
       <c r="B8" t="n">
-        <v>56231</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56884</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1487,15 +1488,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>115822420</v>
+        <v>115822419</v>
       </c>
       <c r="B9" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1527,10 +1523,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>533680</v>
+        <v>533674</v>
       </c>
       <c r="R9" t="n">
-        <v>6531857</v>
+        <v>6531835</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1589,55 +1585,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>115822418</v>
+        <v>115822420</v>
       </c>
       <c r="B10" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Skenebäcksmossen, SV Djupsjön, Regna s:n, Nrk</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>533347</v>
+        <v>533680</v>
       </c>
       <c r="R10" t="n">
-        <v>6531750</v>
+        <v>6531857</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1672,11 +1658,6 @@
           <t>2021-07-25</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Födosöksspår på tall.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1698,6 +1679,103 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>115822646</v>
+      </c>
+      <c r="B11" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Myggsjön, Regna s:n, Nrk</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>533434</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6531571</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Regna</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2021-07-25</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2021-07-25</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Sara Elg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Sara Elg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3902-2024 artfynd.xlsx
+++ b/artfynd/A 3902-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115822418</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -897,6 +907,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99045864</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1020,6 +1035,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101620744</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1138,6 +1158,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101620526</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1261,6 +1286,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101620527</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1384,6 +1414,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101620745</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1485,6 +1520,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115822647</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1582,6 +1622,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115822419</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1679,6 +1724,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115822420</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1776,8 +1826,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115822646</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>